--- a/docs/テーブル定義書.xlsx
+++ b/docs/テーブル定義書.xlsx
@@ -1047,7 +1047,11 @@
       <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="11" t="inlineStr"/>
-      <c r="I9" s="11" t="inlineStr"/>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>中国支社</t>
+        </is>
+      </c>
       <c r="J9" s="11" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr"/>
     </row>
@@ -1074,7 +1078,11 @@
       <c r="F10" s="6" t="inlineStr"/>
       <c r="G10" s="6" t="inlineStr"/>
       <c r="H10" s="13" t="inlineStr"/>
-      <c r="I10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J10" s="13" t="inlineStr"/>
       <c r="K10" s="13" t="inlineStr">
         <is>
@@ -1082,7 +1090,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1" s="14">
+    <row r="11" ht="33.7" customHeight="1" s="14">
       <c r="A11" s="7" t="n">
         <v>4</v>
       </c>
@@ -1109,7 +1117,11 @@
       <c r="F11" s="7" t="inlineStr"/>
       <c r="G11" s="7" t="inlineStr"/>
       <c r="H11" s="11" t="inlineStr"/>
-      <c r="I11" s="11" t="inlineStr"/>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>"HIヒロセスーパーコンボ 元町店"</t>
+        </is>
+      </c>
       <c r="J11" s="11" t="inlineStr"/>
       <c r="K11" s="11" t="inlineStr"/>
     </row>
@@ -1136,7 +1148,9 @@
       <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="13" t="inlineStr"/>
-      <c r="I12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="J12" s="13" t="inlineStr"/>
       <c r="K12" s="13" t="inlineStr">
         <is>
@@ -1167,7 +1181,11 @@
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2F B&amp;C</t>
+        </is>
+      </c>
       <c r="J13" s="11" t="inlineStr"/>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -1198,7 +1216,9 @@
       <c r="F14" s="6" t="inlineStr"/>
       <c r="G14" s="6" t="inlineStr"/>
       <c r="H14" s="13" t="inlineStr"/>
-      <c r="I14" s="13" t="inlineStr"/>
+      <c r="I14" s="13" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="J14" s="13" t="inlineStr"/>
       <c r="K14" s="13" t="inlineStr">
         <is>
@@ -1229,7 +1249,9 @@
       <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr"/>
       <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr"/>
+      <c r="I15" s="11" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="J15" s="11" t="inlineStr"/>
       <c r="K15" s="11" t="inlineStr">
         <is>
@@ -1260,7 +1282,11 @@
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="13" t="inlineStr"/>
-      <c r="I16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J16" s="13" t="inlineStr"/>
       <c r="K16" s="13" t="inlineStr">
         <is>
@@ -1291,7 +1317,11 @@
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="11" t="inlineStr"/>
-      <c r="I17" s="11" t="inlineStr"/>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
       <c r="J17" s="11" t="inlineStr"/>
       <c r="K17" s="11" t="inlineStr">
         <is>
@@ -1322,7 +1352,11 @@
       <c r="F18" s="6" t="inlineStr"/>
       <c r="G18" s="6" t="inlineStr"/>
       <c r="H18" s="13" t="inlineStr"/>
-      <c r="I18" s="13" t="inlineStr"/>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
       <c r="J18" s="13" t="inlineStr"/>
       <c r="K18" s="13" t="inlineStr">
         <is>
@@ -1357,7 +1391,11 @@
       <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr"/>
       <c r="H19" s="11" t="inlineStr"/>
-      <c r="I19" s="11" t="inlineStr"/>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
       <c r="J19" s="11" t="inlineStr"/>
       <c r="K19" s="11" t="inlineStr"/>
     </row>
@@ -1384,7 +1422,11 @@
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="13" t="inlineStr"/>
-      <c r="I20" s="13" t="inlineStr"/>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J20" s="13" t="inlineStr">
         <is>
           <t>前後空白をTRIM。＠/@・中止・確認中→NULL、なし→0。完全未入力行は除外。NULL許容Int64。</t>
@@ -1634,7 +1676,11 @@
       <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="11" t="inlineStr"/>
-      <c r="I9" s="11" t="inlineStr"/>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" s="11" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr">
         <is>
@@ -1704,7 +1750,11 @@
       <c r="F11" s="7" t="inlineStr"/>
       <c r="G11" s="7" t="inlineStr"/>
       <c r="H11" s="11" t="inlineStr"/>
-      <c r="I11" s="11" t="inlineStr"/>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>中国支社</t>
+        </is>
+      </c>
       <c r="J11" s="11" t="inlineStr"/>
       <c r="K11" s="11" t="inlineStr"/>
     </row>
@@ -1739,7 +1789,7 @@
       <c r="J12" s="13" t="inlineStr"/>
       <c r="K12" s="13" t="inlineStr"/>
     </row>
-    <row r="13" ht="20" customHeight="1" s="14">
+    <row r="13" ht="33.7" customHeight="1" s="14">
       <c r="A13" s="7" t="n">
         <v>6</v>
       </c>
@@ -1766,7 +1816,11 @@
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>"HIヒロセスーパーコンボ 元町店"</t>
+        </is>
+      </c>
       <c r="J13" s="11" t="inlineStr"/>
       <c r="K13" s="11" t="inlineStr"/>
     </row>
@@ -2227,7 +2281,11 @@
       <c r="F28" s="6" t="inlineStr"/>
       <c r="G28" s="6" t="inlineStr"/>
       <c r="H28" s="13" t="inlineStr"/>
-      <c r="I28" s="13" t="inlineStr"/>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
       <c r="J28" s="13" t="inlineStr"/>
       <c r="K28" s="13" t="inlineStr">
         <is>
@@ -2258,7 +2316,11 @@
       <c r="F29" s="7" t="inlineStr"/>
       <c r="G29" s="7" t="inlineStr"/>
       <c r="H29" s="11" t="inlineStr"/>
-      <c r="I29" s="11" t="inlineStr"/>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
       <c r="J29" s="11" t="inlineStr"/>
       <c r="K29" s="11" t="inlineStr">
         <is>
@@ -2355,7 +2417,11 @@
       <c r="F32" s="6" t="inlineStr"/>
       <c r="G32" s="6" t="inlineStr"/>
       <c r="H32" s="13" t="inlineStr"/>
-      <c r="I32" s="13" t="inlineStr"/>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
       <c r="J32" s="13" t="inlineStr"/>
       <c r="K32" s="13" t="inlineStr"/>
     </row>
@@ -2386,7 +2452,11 @@
       <c r="F33" s="7" t="inlineStr"/>
       <c r="G33" s="7" t="inlineStr"/>
       <c r="H33" s="11" t="inlineStr"/>
-      <c r="I33" s="11" t="inlineStr"/>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
           <t>正規化前の生値（クレンジング適用前）。</t>
@@ -2417,7 +2487,11 @@
       <c r="F34" s="6" t="inlineStr"/>
       <c r="G34" s="6" t="inlineStr"/>
       <c r="H34" s="13" t="inlineStr"/>
-      <c r="I34" s="13" t="inlineStr"/>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J34" s="13" t="inlineStr">
         <is>
           <t>前後空白をTRIM。＠/@・中止・確認中→NULL、なし→0。完全未入力行は除外。NULL許容Int64。</t>
@@ -2727,7 +2801,11 @@
       <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="11" t="inlineStr"/>
-      <c r="I9" s="11" t="inlineStr"/>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>中国支社</t>
+        </is>
+      </c>
       <c r="J9" s="11" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr"/>
     </row>
@@ -2754,7 +2832,11 @@
       <c r="F10" s="6" t="inlineStr"/>
       <c r="G10" s="6" t="inlineStr"/>
       <c r="H10" s="13" t="inlineStr"/>
-      <c r="I10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J10" s="13" t="inlineStr"/>
       <c r="K10" s="13" t="inlineStr">
         <is>
@@ -2762,7 +2844,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1" s="14">
+    <row r="11" ht="33.7" customHeight="1" s="14">
       <c r="A11" s="7" t="n">
         <v>4</v>
       </c>
@@ -2789,7 +2871,11 @@
       <c r="F11" s="7" t="inlineStr"/>
       <c r="G11" s="7" t="inlineStr"/>
       <c r="H11" s="11" t="inlineStr"/>
-      <c r="I11" s="11" t="inlineStr"/>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>"HIヒロセスーパーコンボ 元町店"</t>
+        </is>
+      </c>
       <c r="J11" s="11" t="inlineStr"/>
       <c r="K11" s="11" t="inlineStr"/>
     </row>
@@ -2816,7 +2902,9 @@
       <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="13" t="inlineStr"/>
-      <c r="I12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="J12" s="13" t="inlineStr"/>
       <c r="K12" s="13" t="inlineStr">
         <is>
@@ -2847,7 +2935,11 @@
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2F B&amp;C</t>
+        </is>
+      </c>
       <c r="J13" s="11" t="inlineStr"/>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -2878,7 +2970,9 @@
       <c r="F14" s="6" t="inlineStr"/>
       <c r="G14" s="6" t="inlineStr"/>
       <c r="H14" s="13" t="inlineStr"/>
-      <c r="I14" s="13" t="inlineStr"/>
+      <c r="I14" s="13" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="J14" s="13" t="inlineStr"/>
       <c r="K14" s="13" t="inlineStr">
         <is>
@@ -2909,7 +3003,9 @@
       <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr"/>
       <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr"/>
+      <c r="I15" s="11" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="J15" s="11" t="inlineStr"/>
       <c r="K15" s="11" t="inlineStr">
         <is>
@@ -2940,7 +3036,11 @@
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="13" t="inlineStr"/>
-      <c r="I16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J16" s="13" t="inlineStr"/>
       <c r="K16" s="13" t="inlineStr">
         <is>
@@ -2971,7 +3071,11 @@
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="11" t="inlineStr"/>
-      <c r="I17" s="11" t="inlineStr"/>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
       <c r="J17" s="11" t="inlineStr"/>
       <c r="K17" s="11" t="inlineStr">
         <is>
@@ -3002,7 +3106,11 @@
       <c r="F18" s="6" t="inlineStr"/>
       <c r="G18" s="6" t="inlineStr"/>
       <c r="H18" s="13" t="inlineStr"/>
-      <c r="I18" s="13" t="inlineStr"/>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
       <c r="J18" s="13" t="inlineStr"/>
       <c r="K18" s="13" t="inlineStr">
         <is>
@@ -3037,7 +3145,11 @@
       <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr"/>
       <c r="H19" s="11" t="inlineStr"/>
-      <c r="I19" s="11" t="inlineStr"/>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
       <c r="J19" s="11" t="inlineStr"/>
       <c r="K19" s="11" t="inlineStr"/>
     </row>
@@ -3064,7 +3176,11 @@
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="13" t="inlineStr"/>
-      <c r="I20" s="13" t="inlineStr"/>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J20" s="13" t="inlineStr"/>
       <c r="K20" s="13" t="inlineStr">
         <is>
@@ -3275,7 +3391,11 @@
       <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="13" t="inlineStr"/>
-      <c r="I8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" s="13" t="inlineStr"/>
       <c r="K8" s="13" t="inlineStr"/>
     </row>
@@ -3306,7 +3426,11 @@
       <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="11" t="inlineStr"/>
-      <c r="I9" s="11" t="inlineStr"/>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>BRANCH博多パピヨンガーデン</t>
+        </is>
+      </c>
       <c r="J9" s="11" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr"/>
     </row>
@@ -3407,7 +3531,11 @@
       <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="13" t="inlineStr"/>
-      <c r="I12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J12" s="13" t="inlineStr"/>
       <c r="K12" s="13" t="inlineStr"/>
     </row>
@@ -3438,7 +3566,11 @@
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
       <c r="J13" s="11" t="inlineStr"/>
       <c r="K13" s="11" t="inlineStr"/>
     </row>
@@ -3539,7 +3671,11 @@
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="13" t="inlineStr"/>
-      <c r="I16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J16" s="13" t="inlineStr"/>
       <c r="K16" s="13" t="inlineStr"/>
     </row>
@@ -3706,7 +3842,11 @@
       <c r="F21" s="7" t="inlineStr"/>
       <c r="G21" s="7" t="inlineStr"/>
       <c r="H21" s="11" t="inlineStr"/>
-      <c r="I21" s="11" t="inlineStr"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J21" s="11" t="inlineStr"/>
       <c r="K21" s="11" t="inlineStr">
         <is>
@@ -4447,7 +4587,11 @@
       <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="13" t="inlineStr"/>
-      <c r="I12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" s="13" t="inlineStr"/>
       <c r="K12" s="13" t="inlineStr"/>
     </row>
@@ -4478,7 +4622,11 @@
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>BRANCH博多パピヨンガーデン</t>
+        </is>
+      </c>
       <c r="J13" s="11" t="inlineStr"/>
       <c r="K13" s="11" t="inlineStr"/>
     </row>
@@ -4579,7 +4727,11 @@
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="13" t="inlineStr"/>
-      <c r="I16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J16" s="13" t="inlineStr"/>
       <c r="K16" s="13" t="inlineStr"/>
     </row>
@@ -4680,7 +4832,11 @@
       <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr"/>
       <c r="H19" s="11" t="inlineStr"/>
-      <c r="I19" s="11" t="inlineStr"/>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J19" s="11" t="inlineStr"/>
       <c r="K19" s="11" t="inlineStr"/>
     </row>
@@ -4707,7 +4863,11 @@
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="13" t="inlineStr"/>
-      <c r="I20" s="13" t="inlineStr"/>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J20" s="13" t="inlineStr"/>
       <c r="K20" s="13" t="inlineStr">
         <is>
@@ -4738,7 +4898,11 @@
       <c r="F21" s="7" t="inlineStr"/>
       <c r="G21" s="7" t="inlineStr"/>
       <c r="H21" s="11" t="inlineStr"/>
-      <c r="I21" s="11" t="inlineStr"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J21" s="11" t="inlineStr"/>
       <c r="K21" s="11" t="inlineStr">
         <is>
@@ -5228,7 +5392,11 @@
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="13" t="inlineStr"/>
-      <c r="I16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J16" s="13" t="inlineStr"/>
       <c r="K16" s="13" t="inlineStr"/>
     </row>
@@ -5259,7 +5427,11 @@
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="11" t="inlineStr"/>
-      <c r="I17" s="11" t="inlineStr"/>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J17" s="11" t="inlineStr"/>
       <c r="K17" s="11" t="inlineStr"/>
     </row>
@@ -5290,7 +5462,11 @@
       <c r="F18" s="6" t="inlineStr"/>
       <c r="G18" s="6" t="inlineStr"/>
       <c r="H18" s="13" t="inlineStr"/>
-      <c r="I18" s="13" t="inlineStr"/>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J18" s="13" t="inlineStr"/>
       <c r="K18" s="13" t="inlineStr"/>
     </row>
@@ -5321,7 +5497,11 @@
       <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr"/>
       <c r="H19" s="11" t="inlineStr"/>
-      <c r="I19" s="11" t="inlineStr"/>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J19" s="11" t="inlineStr"/>
       <c r="K19" s="11" t="inlineStr"/>
     </row>
@@ -5352,7 +5532,11 @@
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="13" t="inlineStr"/>
-      <c r="I20" s="13" t="inlineStr"/>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J20" s="13" t="inlineStr"/>
       <c r="K20" s="13" t="inlineStr"/>
     </row>
@@ -5383,7 +5567,11 @@
       <c r="F21" s="7" t="inlineStr"/>
       <c r="G21" s="7" t="inlineStr"/>
       <c r="H21" s="11" t="inlineStr"/>
-      <c r="I21" s="11" t="inlineStr"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J21" s="11" t="inlineStr"/>
       <c r="K21" s="11" t="inlineStr"/>
     </row>
@@ -5414,7 +5602,11 @@
       <c r="F22" s="6" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr"/>
       <c r="H22" s="13" t="inlineStr"/>
-      <c r="I22" s="13" t="inlineStr"/>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J22" s="13" t="inlineStr"/>
       <c r="K22" s="13" t="inlineStr"/>
     </row>
@@ -5445,7 +5637,11 @@
       <c r="F23" s="7" t="inlineStr"/>
       <c r="G23" s="7" t="inlineStr"/>
       <c r="H23" s="11" t="inlineStr"/>
-      <c r="I23" s="11" t="inlineStr"/>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J23" s="11" t="inlineStr"/>
       <c r="K23" s="11" t="inlineStr"/>
     </row>
@@ -5476,7 +5672,11 @@
       <c r="F24" s="6" t="inlineStr"/>
       <c r="G24" s="6" t="inlineStr"/>
       <c r="H24" s="13" t="inlineStr"/>
-      <c r="I24" s="13" t="inlineStr"/>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J24" s="13" t="inlineStr"/>
       <c r="K24" s="13" t="inlineStr"/>
     </row>
@@ -5681,7 +5881,11 @@
       <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="13" t="inlineStr"/>
-      <c r="I8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" s="13" t="inlineStr"/>
       <c r="K8" s="13" t="inlineStr"/>
     </row>
@@ -5712,7 +5916,11 @@
       <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="11" t="inlineStr"/>
-      <c r="I9" s="11" t="inlineStr"/>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>BRANCH博多パピヨンガーデン</t>
+        </is>
+      </c>
       <c r="J9" s="11" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr"/>
     </row>
@@ -6032,7 +6240,11 @@
       <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="13" t="inlineStr"/>
-      <c r="I8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" s="13" t="inlineStr"/>
       <c r="K8" s="13" t="inlineStr"/>
     </row>
@@ -6063,7 +6275,11 @@
       <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="11" t="inlineStr"/>
-      <c r="I9" s="11" t="inlineStr"/>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>BRANCH博多パピヨンガーデン</t>
+        </is>
+      </c>
       <c r="J9" s="11" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr"/>
     </row>
@@ -6187,7 +6403,11 @@
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
       <c r="J13" s="11" t="inlineStr"/>
       <c r="K13" s="11" t="inlineStr"/>
     </row>
@@ -6401,7 +6621,11 @@
       <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="13" t="inlineStr"/>
-      <c r="I8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" s="13" t="inlineStr"/>
       <c r="K8" s="13" t="inlineStr"/>
     </row>
@@ -6432,7 +6656,11 @@
       <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="11" t="inlineStr"/>
-      <c r="I9" s="11" t="inlineStr"/>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>BRANCH博多パピヨンガーデン</t>
+        </is>
+      </c>
       <c r="J9" s="11" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr"/>
     </row>
@@ -7286,7 +7514,11 @@
       <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="13" t="inlineStr"/>
-      <c r="I12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" s="13" t="inlineStr"/>
       <c r="K12" s="13" t="inlineStr"/>
     </row>
@@ -7317,7 +7549,11 @@
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>BRANCH博多パピヨンガーデン</t>
+        </is>
+      </c>
       <c r="J13" s="11" t="inlineStr"/>
       <c r="K13" s="11" t="inlineStr"/>
     </row>
@@ -7418,7 +7654,9 @@
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="13" t="inlineStr"/>
-      <c r="I16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="J16" s="13" t="inlineStr"/>
       <c r="K16" s="13" t="inlineStr"/>
     </row>
@@ -7515,7 +7753,11 @@
       <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr"/>
       <c r="H19" s="11" t="inlineStr"/>
-      <c r="I19" s="11" t="inlineStr"/>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J19" s="11" t="inlineStr"/>
       <c r="K19" s="11" t="inlineStr">
         <is>
@@ -7546,7 +7788,11 @@
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="13" t="inlineStr"/>
-      <c r="I20" s="13" t="inlineStr"/>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J20" s="13" t="inlineStr"/>
       <c r="K20" s="13" t="inlineStr">
         <is>
@@ -7577,7 +7823,11 @@
       <c r="F21" s="7" t="inlineStr"/>
       <c r="G21" s="7" t="inlineStr"/>
       <c r="H21" s="11" t="inlineStr"/>
-      <c r="I21" s="11" t="inlineStr"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J21" s="11" t="inlineStr"/>
       <c r="K21" s="11" t="inlineStr">
         <is>
@@ -7608,7 +7858,11 @@
       <c r="F22" s="6" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr"/>
       <c r="H22" s="13" t="inlineStr"/>
-      <c r="I22" s="13" t="inlineStr"/>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J22" s="13" t="inlineStr"/>
       <c r="K22" s="13" t="inlineStr">
         <is>
@@ -7639,7 +7893,11 @@
       <c r="F23" s="7" t="inlineStr"/>
       <c r="G23" s="7" t="inlineStr"/>
       <c r="H23" s="11" t="inlineStr"/>
-      <c r="I23" s="11" t="inlineStr"/>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J23" s="11" t="inlineStr"/>
       <c r="K23" s="11" t="inlineStr">
         <is>
@@ -7670,7 +7928,11 @@
       <c r="F24" s="6" t="inlineStr"/>
       <c r="G24" s="6" t="inlineStr"/>
       <c r="H24" s="13" t="inlineStr"/>
-      <c r="I24" s="13" t="inlineStr"/>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" s="13" t="inlineStr"/>
       <c r="K24" s="13" t="inlineStr">
         <is>
@@ -7701,7 +7963,11 @@
       <c r="F25" s="7" t="inlineStr"/>
       <c r="G25" s="7" t="inlineStr"/>
       <c r="H25" s="11" t="inlineStr"/>
-      <c r="I25" s="11" t="inlineStr"/>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J25" s="11" t="inlineStr"/>
       <c r="K25" s="11" t="inlineStr">
         <is>
@@ -7732,7 +7998,11 @@
       <c r="F26" s="6" t="inlineStr"/>
       <c r="G26" s="6" t="inlineStr"/>
       <c r="H26" s="13" t="inlineStr"/>
-      <c r="I26" s="13" t="inlineStr"/>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J26" s="13" t="inlineStr"/>
       <c r="K26" s="13" t="inlineStr">
         <is>
@@ -7763,7 +8033,11 @@
       <c r="F27" s="7" t="inlineStr"/>
       <c r="G27" s="7" t="inlineStr"/>
       <c r="H27" s="11" t="inlineStr"/>
-      <c r="I27" s="11" t="inlineStr"/>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J27" s="11" t="inlineStr"/>
       <c r="K27" s="11" t="inlineStr">
         <is>
@@ -7794,7 +8068,11 @@
       <c r="F28" s="6" t="inlineStr"/>
       <c r="G28" s="6" t="inlineStr"/>
       <c r="H28" s="13" t="inlineStr"/>
-      <c r="I28" s="13" t="inlineStr"/>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J28" s="13" t="inlineStr"/>
       <c r="K28" s="13" t="inlineStr">
         <is>
@@ -8143,7 +8421,11 @@
       <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="13" t="inlineStr"/>
-      <c r="I12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" s="13" t="inlineStr"/>
       <c r="K12" s="13" t="inlineStr"/>
     </row>
@@ -8174,7 +8456,11 @@
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>BRANCH博多パピヨンガーデン</t>
+        </is>
+      </c>
       <c r="J13" s="11" t="inlineStr"/>
       <c r="K13" s="11" t="inlineStr"/>
     </row>
@@ -8275,7 +8561,9 @@
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="13" t="inlineStr"/>
-      <c r="I16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="J16" s="13" t="inlineStr"/>
       <c r="K16" s="13" t="inlineStr"/>
     </row>
@@ -8407,7 +8695,11 @@
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="13" t="inlineStr"/>
-      <c r="I20" s="13" t="inlineStr"/>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" s="13" t="inlineStr"/>
       <c r="K20" s="13" t="inlineStr">
         <is>
@@ -8438,7 +8730,11 @@
       <c r="F21" s="7" t="inlineStr"/>
       <c r="G21" s="7" t="inlineStr"/>
       <c r="H21" s="11" t="inlineStr"/>
-      <c r="I21" s="11" t="inlineStr"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J21" s="11" t="inlineStr"/>
       <c r="K21" s="11" t="inlineStr">
         <is>
@@ -8469,7 +8765,11 @@
       <c r="F22" s="6" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr"/>
       <c r="H22" s="13" t="inlineStr"/>
-      <c r="I22" s="13" t="inlineStr"/>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J22" s="13" t="inlineStr"/>
       <c r="K22" s="13" t="inlineStr">
         <is>
@@ -8500,7 +8800,11 @@
       <c r="F23" s="7" t="inlineStr"/>
       <c r="G23" s="7" t="inlineStr"/>
       <c r="H23" s="11" t="inlineStr"/>
-      <c r="I23" s="11" t="inlineStr"/>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J23" s="11" t="inlineStr"/>
       <c r="K23" s="11" t="inlineStr">
         <is>
@@ -8531,7 +8835,11 @@
       <c r="F24" s="6" t="inlineStr"/>
       <c r="G24" s="6" t="inlineStr"/>
       <c r="H24" s="13" t="inlineStr"/>
-      <c r="I24" s="13" t="inlineStr"/>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" s="13" t="inlineStr"/>
       <c r="K24" s="13" t="inlineStr">
         <is>
@@ -8562,7 +8870,11 @@
       <c r="F25" s="7" t="inlineStr"/>
       <c r="G25" s="7" t="inlineStr"/>
       <c r="H25" s="11" t="inlineStr"/>
-      <c r="I25" s="11" t="inlineStr"/>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J25" s="11" t="inlineStr"/>
       <c r="K25" s="11" t="inlineStr">
         <is>
@@ -8911,7 +9223,11 @@
       <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="13" t="inlineStr"/>
-      <c r="I12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" s="13" t="inlineStr"/>
       <c r="K12" s="13" t="inlineStr"/>
     </row>
@@ -8942,7 +9258,11 @@
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>BRANCH博多パピヨンガーデン</t>
+        </is>
+      </c>
       <c r="J13" s="11" t="inlineStr"/>
       <c r="K13" s="11" t="inlineStr"/>
     </row>
@@ -9043,7 +9363,9 @@
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="13" t="inlineStr"/>
-      <c r="I16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="J16" s="13" t="inlineStr"/>
       <c r="K16" s="13" t="inlineStr"/>
     </row>
@@ -9179,7 +9501,11 @@
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="13" t="inlineStr"/>
-      <c r="I20" s="13" t="inlineStr"/>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" s="13" t="inlineStr"/>
       <c r="K20" s="13" t="inlineStr"/>
     </row>
@@ -9210,7 +9536,11 @@
       <c r="F21" s="7" t="inlineStr"/>
       <c r="G21" s="7" t="inlineStr"/>
       <c r="H21" s="11" t="inlineStr"/>
-      <c r="I21" s="11" t="inlineStr"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J21" s="11" t="inlineStr"/>
       <c r="K21" s="11" t="inlineStr"/>
     </row>
@@ -9241,7 +9571,11 @@
       <c r="F22" s="6" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr"/>
       <c r="H22" s="13" t="inlineStr"/>
-      <c r="I22" s="13" t="inlineStr"/>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J22" s="13" t="inlineStr"/>
       <c r="K22" s="13" t="inlineStr"/>
     </row>
@@ -9272,7 +9606,11 @@
       <c r="F23" s="7" t="inlineStr"/>
       <c r="G23" s="7" t="inlineStr"/>
       <c r="H23" s="11" t="inlineStr"/>
-      <c r="I23" s="11" t="inlineStr"/>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J23" s="11" t="inlineStr"/>
       <c r="K23" s="11" t="inlineStr"/>
     </row>
@@ -9303,7 +9641,11 @@
       <c r="F24" s="6" t="inlineStr"/>
       <c r="G24" s="6" t="inlineStr"/>
       <c r="H24" s="13" t="inlineStr"/>
-      <c r="I24" s="13" t="inlineStr"/>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J24" s="13" t="inlineStr"/>
       <c r="K24" s="13" t="inlineStr"/>
     </row>
@@ -9334,7 +9676,11 @@
       <c r="F25" s="7" t="inlineStr"/>
       <c r="G25" s="7" t="inlineStr"/>
       <c r="H25" s="11" t="inlineStr"/>
-      <c r="I25" s="11" t="inlineStr"/>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J25" s="11" t="inlineStr"/>
       <c r="K25" s="11" t="inlineStr"/>
     </row>
@@ -9679,7 +10025,11 @@
       <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="13" t="inlineStr"/>
-      <c r="I12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" s="13" t="inlineStr"/>
       <c r="K12" s="13" t="inlineStr"/>
     </row>
@@ -9710,7 +10060,11 @@
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>BRANCH博多パピヨンガーデン</t>
+        </is>
+      </c>
       <c r="J13" s="11" t="inlineStr"/>
       <c r="K13" s="11" t="inlineStr"/>
     </row>
@@ -9811,7 +10165,9 @@
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="13" t="inlineStr"/>
-      <c r="I16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="J16" s="13" t="inlineStr"/>
       <c r="K16" s="13" t="inlineStr"/>
     </row>
@@ -9842,7 +10198,11 @@
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="11" t="inlineStr"/>
-      <c r="I17" s="11" t="inlineStr"/>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
       <c r="J17" s="11" t="inlineStr"/>
       <c r="K17" s="11" t="inlineStr"/>
     </row>
@@ -9974,7 +10334,11 @@
       <c r="F21" s="7" t="inlineStr"/>
       <c r="G21" s="7" t="inlineStr"/>
       <c r="H21" s="11" t="inlineStr"/>
-      <c r="I21" s="11" t="inlineStr"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J21" s="11" t="inlineStr"/>
       <c r="K21" s="11" t="inlineStr">
         <is>
@@ -10005,7 +10369,11 @@
       <c r="F22" s="6" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr"/>
       <c r="H22" s="13" t="inlineStr"/>
-      <c r="I22" s="13" t="inlineStr"/>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J22" s="13" t="inlineStr"/>
       <c r="K22" s="13" t="inlineStr">
         <is>
@@ -10036,7 +10404,11 @@
       <c r="F23" s="7" t="inlineStr"/>
       <c r="G23" s="7" t="inlineStr"/>
       <c r="H23" s="11" t="inlineStr"/>
-      <c r="I23" s="11" t="inlineStr"/>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J23" s="11" t="inlineStr"/>
       <c r="K23" s="11" t="inlineStr">
         <is>
@@ -10067,7 +10439,11 @@
       <c r="F24" s="6" t="inlineStr"/>
       <c r="G24" s="6" t="inlineStr"/>
       <c r="H24" s="13" t="inlineStr"/>
-      <c r="I24" s="13" t="inlineStr"/>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" s="13" t="inlineStr"/>
       <c r="K24" s="13" t="inlineStr">
         <is>
@@ -10098,7 +10474,11 @@
       <c r="F25" s="7" t="inlineStr"/>
       <c r="G25" s="7" t="inlineStr"/>
       <c r="H25" s="11" t="inlineStr"/>
-      <c r="I25" s="11" t="inlineStr"/>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J25" s="11" t="inlineStr"/>
       <c r="K25" s="11" t="inlineStr">
         <is>
@@ -10129,7 +10509,11 @@
       <c r="F26" s="6" t="inlineStr"/>
       <c r="G26" s="6" t="inlineStr"/>
       <c r="H26" s="13" t="inlineStr"/>
-      <c r="I26" s="13" t="inlineStr"/>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J26" s="13" t="inlineStr"/>
       <c r="K26" s="13" t="inlineStr">
         <is>
@@ -10350,7 +10734,11 @@
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr"/>
-      <c r="I8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" s="13" t="inlineStr"/>
       <c r="K8" s="13" t="inlineStr"/>
     </row>
@@ -10389,7 +10777,11 @@
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr"/>
-      <c r="I9" s="11" t="inlineStr"/>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>BRANCH博多パピヨンガーデン</t>
+        </is>
+      </c>
       <c r="J9" s="11" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr"/>
     </row>
@@ -10490,7 +10882,9 @@
       <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="13" t="inlineStr"/>
-      <c r="I12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="J12" s="13" t="inlineStr"/>
       <c r="K12" s="13" t="inlineStr"/>
     </row>
@@ -10713,7 +11107,11 @@
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr"/>
-      <c r="I8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
       <c r="J8" s="13" t="inlineStr"/>
       <c r="K8" s="13" t="inlineStr"/>
     </row>
@@ -10752,7 +11150,11 @@
           <t>raw_facility_master.facility_code</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr"/>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" s="11" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr"/>
     </row>
@@ -10783,7 +11185,11 @@
       <c r="F10" s="6" t="inlineStr"/>
       <c r="G10" s="6" t="inlineStr"/>
       <c r="H10" s="13" t="inlineStr"/>
-      <c r="I10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>BRANCH博多パピヨンガーデン</t>
+        </is>
+      </c>
       <c r="J10" s="13" t="inlineStr"/>
       <c r="K10" s="13" t="inlineStr"/>
     </row>
@@ -10814,7 +11220,11 @@
       <c r="F11" s="7" t="inlineStr"/>
       <c r="G11" s="7" t="inlineStr"/>
       <c r="H11" s="11" t="inlineStr"/>
-      <c r="I11" s="11" t="inlineStr"/>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
       <c r="J11" s="11" t="inlineStr"/>
       <c r="K11" s="11" t="inlineStr"/>
     </row>
@@ -11148,7 +11558,11 @@
           <t>raw_facility_master.facility_code</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" s="13" t="inlineStr"/>
       <c r="K8" s="13" t="inlineStr"/>
     </row>
@@ -11187,7 +11601,11 @@
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr"/>
-      <c r="I9" s="11" t="inlineStr"/>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>BRANCH博多パピヨンガーデン</t>
+        </is>
+      </c>
       <c r="J9" s="11" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr"/>
     </row>
@@ -11218,7 +11636,11 @@
       <c r="F10" s="6" t="inlineStr"/>
       <c r="G10" s="6" t="inlineStr"/>
       <c r="H10" s="13" t="inlineStr"/>
-      <c r="I10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J10" s="13" t="inlineStr"/>
       <c r="K10" s="13" t="inlineStr"/>
     </row>
@@ -11249,7 +11671,11 @@
       <c r="F11" s="7" t="inlineStr"/>
       <c r="G11" s="7" t="inlineStr"/>
       <c r="H11" s="11" t="inlineStr"/>
-      <c r="I11" s="11" t="inlineStr"/>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J11" s="11" t="inlineStr"/>
       <c r="K11" s="11" t="inlineStr"/>
     </row>
@@ -11280,7 +11706,11 @@
       <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="13" t="inlineStr"/>
-      <c r="I12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="J12" s="13" t="inlineStr"/>
       <c r="K12" s="13" t="inlineStr"/>
     </row>
@@ -11311,7 +11741,11 @@
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J13" s="11" t="inlineStr"/>
       <c r="K13" s="11" t="inlineStr"/>
     </row>
@@ -11342,7 +11776,11 @@
       <c r="F14" s="6" t="inlineStr"/>
       <c r="G14" s="6" t="inlineStr"/>
       <c r="H14" s="13" t="inlineStr"/>
-      <c r="I14" s="13" t="inlineStr"/>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="J14" s="13" t="inlineStr"/>
       <c r="K14" s="13" t="inlineStr"/>
     </row>
@@ -11373,7 +11811,11 @@
       <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr"/>
       <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr"/>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J15" s="11" t="inlineStr"/>
       <c r="K15" s="11" t="inlineStr"/>
     </row>
@@ -11404,7 +11846,11 @@
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="13" t="inlineStr"/>
-      <c r="I16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="J16" s="13" t="inlineStr"/>
       <c r="K16" s="13" t="inlineStr"/>
     </row>
@@ -11435,7 +11881,11 @@
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="11" t="inlineStr"/>
-      <c r="I17" s="11" t="inlineStr"/>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
       <c r="J17" s="11" t="inlineStr"/>
       <c r="K17" s="11" t="inlineStr"/>
     </row>
@@ -11466,7 +11916,11 @@
       <c r="F18" s="6" t="inlineStr"/>
       <c r="G18" s="6" t="inlineStr"/>
       <c r="H18" s="13" t="inlineStr"/>
-      <c r="I18" s="13" t="inlineStr"/>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J18" s="13" t="inlineStr"/>
       <c r="K18" s="13" t="inlineStr"/>
     </row>
@@ -11998,7 +12452,11 @@
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr"/>
-      <c r="I8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
       <c r="J8" s="13" t="inlineStr"/>
       <c r="K8" s="13" t="inlineStr"/>
     </row>
@@ -12029,7 +12487,11 @@
       <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="11" t="inlineStr"/>
-      <c r="I9" s="11" t="inlineStr"/>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>2025/10</t>
+        </is>
+      </c>
       <c r="J9" s="11" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr"/>
     </row>
@@ -12130,7 +12592,11 @@
       <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="13" t="inlineStr"/>
-      <c r="I12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" s="13" t="inlineStr"/>
       <c r="K12" s="13" t="inlineStr"/>
     </row>
@@ -12161,7 +12627,11 @@
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" s="11" t="inlineStr"/>
       <c r="K13" s="11" t="inlineStr"/>
     </row>
@@ -12262,7 +12732,11 @@
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr"/>
       <c r="H16" s="13" t="inlineStr"/>
-      <c r="I16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>土（1）</t>
+        </is>
+      </c>
       <c r="J16" s="13" t="inlineStr"/>
       <c r="K16" s="13" t="inlineStr"/>
     </row>
@@ -12359,7 +12833,11 @@
       <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr"/>
       <c r="H19" s="11" t="inlineStr"/>
-      <c r="I19" s="11" t="inlineStr"/>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>こどもの日</t>
+        </is>
+      </c>
       <c r="J19" s="11" t="inlineStr"/>
       <c r="K19" s="11" t="inlineStr">
         <is>
@@ -12720,7 +13198,11 @@
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr"/>
-      <c r="I8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
       <c r="J8" s="13" t="inlineStr"/>
       <c r="K8" s="13" t="inlineStr"/>
     </row>
@@ -12786,7 +13268,11 @@
       <c r="F10" s="6" t="inlineStr"/>
       <c r="G10" s="6" t="inlineStr"/>
       <c r="H10" s="13" t="inlineStr"/>
-      <c r="I10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" s="13" t="inlineStr"/>
       <c r="K10" s="13" t="inlineStr"/>
     </row>
@@ -12887,7 +13373,11 @@
       </c>
       <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>こどもの日</t>
+        </is>
+      </c>
       <c r="J13" s="11" t="inlineStr"/>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -13321,7 +13811,11 @@
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr"/>
-      <c r="I8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
       <c r="J8" s="13" t="inlineStr"/>
       <c r="K8" s="13" t="inlineStr"/>
     </row>
@@ -13387,7 +13881,11 @@
       <c r="F10" s="6" t="inlineStr"/>
       <c r="G10" s="6" t="inlineStr"/>
       <c r="H10" s="13" t="inlineStr"/>
-      <c r="I10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" s="13" t="inlineStr"/>
       <c r="K10" s="13" t="inlineStr"/>
     </row>
@@ -13488,7 +13986,11 @@
       </c>
       <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr"/>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>こどもの日</t>
+        </is>
+      </c>
       <c r="J13" s="11" t="inlineStr"/>
       <c r="K13" s="11" t="inlineStr">
         <is>
@@ -13914,7 +14416,11 @@
       <c r="F8" s="6" t="inlineStr"/>
       <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="13" t="inlineStr"/>
-      <c r="I8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>Ao（アオ）</t>
+        </is>
+      </c>
       <c r="J8" s="13" t="inlineStr"/>
       <c r="K8" s="13" t="inlineStr"/>
     </row>
@@ -13945,7 +14451,11 @@
       <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="11" t="inlineStr"/>
-      <c r="I9" s="11" t="inlineStr"/>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>BRANCH博多パピヨンガーデン</t>
+        </is>
+      </c>
       <c r="J9" s="11" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr"/>
     </row>

--- a/docs/テーブル定義書.xlsx
+++ b/docs/テーブル定義書.xlsx
@@ -38,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -97,6 +97,12 @@
       <family val="3"/>
       <sz val="6"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <color rgb="000563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="6">
@@ -211,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -273,6 +279,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -822,7 +831,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1455,7 +1464,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2580,7 +2589,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="0000B0F0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3205,7 +3214,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="0000B0F0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3870,7 +3879,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="0000B0F0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4261,7 +4270,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="0000B0F0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4926,7 +4935,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="0000B0F0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -5695,7 +5704,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="0000B0F0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6054,7 +6063,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="0000B0F0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6435,7 +6444,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="0000B0F0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6764,13 +6773,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="5" customWidth="1" style="14" min="1" max="1"/>
     <col width="48" customWidth="1" style="14" min="2" max="2"/>
     <col width="24" customWidth="1" style="14" min="3" max="3"/>
     <col width="56" customWidth="1" style="14" min="4" max="4"/>
+    <col width="16" customWidth="1" style="14" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="52.60000000000001" customHeight="1" s="14">
@@ -6802,6 +6812,11 @@
           <t>用途・概要</t>
         </is>
       </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>リンク</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="33.7" customHeight="1" s="14">
       <c r="A4" s="6" t="n">
@@ -6822,6 +6837,11 @@
           <t>施設マスタのrawモデル。スプレッドシート由来の施設情報を保持する。</t>
         </is>
       </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="33.7" customHeight="1" s="14">
       <c r="A5" s="7" t="n">
@@ -6842,6 +6862,11 @@
           <t>施設別・日別の偏差値ベースZスコアrawモデル</t>
         </is>
       </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="48.55" customHeight="1" s="14">
       <c r="A6" s="6" t="n">
@@ -6862,6 +6887,11 @@
           <t>施設別・日付フラグ別の人流合計およびデシル区分rawモデル</t>
         </is>
       </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="14">
       <c r="A7" s="7" t="n">
@@ -6882,6 +6912,11 @@
           <t>日付マスタのrawモデル</t>
         </is>
       </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="14">
       <c r="A8" s="6" t="n">
@@ -6902,6 +6937,11 @@
           <t>日付マスタのrawモデル</t>
         </is>
       </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1" s="14">
       <c r="A9" s="7" t="n">
@@ -6922,6 +6962,11 @@
           <t>日付マスタのrawモデル</t>
         </is>
       </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="33.7" customHeight="1" s="14">
       <c r="A10" s="6" t="n">
@@ -6942,6 +6987,11 @@
           <t>施設名マッピングのrawモデル。施設名の表記ゆれを統一するためのマッピング情報を保持する。</t>
         </is>
       </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="33.7" customHeight="1" s="14">
       <c r="A11" s="7" t="n">
@@ -6962,6 +7012,11 @@
           <t>施設別・日付別実績のrawモデル</t>
         </is>
       </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1" s="14">
       <c r="A12" s="6" t="n">
@@ -6982,6 +7037,11 @@
           <t>会場別・日別実績のrawモデル</t>
         </is>
       </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18.85" customHeight="1" s="14">
       <c r="A13" s="7" t="n">
@@ -6998,6 +7058,11 @@
           <t>施設別・日付別実績のintermediateモデル</t>
         </is>
       </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="33.7" customHeight="1" s="14">
       <c r="A14" s="6" t="n">
@@ -7014,6 +7079,11 @@
           <t>施設別・日別実績に施設属性と日付属性を付与したintermediateモデル</t>
         </is>
       </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18.85" customHeight="1" s="14">
       <c r="A15" s="7" t="n">
@@ -7030,6 +7100,11 @@
           <t>ベンチマーク期間を定義するintermediateモデル</t>
         </is>
       </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="33.7" customHeight="1" s="14">
       <c r="A16" s="6" t="n">
@@ -7046,6 +7121,11 @@
           <t>施設・月・月内週番号・日付フラグ・デシル区分ごとの平均実績intermediateモデル</t>
         </is>
       </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="33.7" customHeight="1" s="14">
       <c r="A17" s="7" t="n">
@@ -7062,6 +7142,11 @@
           <t>月・月内週番号・日付フラグ・デシル区分ごとの実績分位点を施設別に付与したintermediateモデル</t>
         </is>
       </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="33.7" customHeight="1" s="14">
       <c r="A18" s="6" t="n">
@@ -7078,6 +7163,11 @@
           <t>施設・月・日付フラグごとのZスコアの平均を算出したintermediateモデル</t>
         </is>
       </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="33.7" customHeight="1" s="14">
       <c r="A19" s="7" t="n">
@@ -7094,6 +7184,11 @@
           <t>施設・月・曜日・日付フラグごとのZスコアの平均を算出したintermediateモデル</t>
         </is>
       </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="33.7" customHeight="1" s="14">
       <c r="A20" s="6" t="n">
@@ -7110,6 +7205,11 @@
           <t>施設・月・月内週番号・日付フラグごとのデシルランク割当intermediateモデル</t>
         </is>
       </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="33.7" customHeight="1" s="14">
       <c r="A21" s="7" t="n">
@@ -7126,6 +7226,11 @@
           <t>施設・月・月内週番号・日付フラグごとの標準目標値とチャレンジ目標値を算出するintermediateモデル</t>
         </is>
       </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="33.7" customHeight="1" s="14">
       <c r="A22" s="6" t="n">
@@ -7142,6 +7247,11 @@
           <t>日別の目標値を施設*月*週番号*日付フラグ粒度で格納するファクトテーブル</t>
         </is>
       </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="33.7" customHeight="1" s="14">
       <c r="A23" s="7" t="n">
@@ -7158,6 +7268,11 @@
           <t>2025年と2026年の日別の目標値を施設*月*週番号*日付フラグ粒度で格納するファクトテーブル</t>
         </is>
       </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="18.85" customHeight="1" s="14">
       <c r="A24" s="6" t="n">
@@ -7174,12 +7289,40 @@
           <t>2026年と2027年の日別の目標値を格納するファクトテーブル</t>
         </is>
       </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>テーブル定義書</t>
+        </is>
+      </c>
     </row>
     <row r="25"/>
     <row r="26">
       <c r="A26" s="9" t="n"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -7188,7 +7331,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="0000B0F0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -8095,7 +8238,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -8897,7 +9040,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -9699,7 +9842,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -10536,7 +10679,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -10913,7 +11056,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -11356,7 +11499,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -12254,7 +12397,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -13000,7 +13143,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -13613,7 +13756,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -14226,7 +14369,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF305496"/>
+    <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/docs/テーブル定義書.xlsx
+++ b/docs/テーブル定義書.xlsx
@@ -217,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -279,8 +279,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6862,7 +6865,7 @@
           <t>施設別・日別の偏差値ベースZスコアrawモデル</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -6912,7 +6915,7 @@
           <t>日付マスタのrawモデル</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -6962,7 +6965,7 @@
           <t>日付マスタのrawモデル</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7012,7 +7015,7 @@
           <t>施設別・日付別実績のrawモデル</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7058,7 +7061,7 @@
           <t>施設別・日付別実績のintermediateモデル</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7100,7 +7103,7 @@
           <t>ベンチマーク期間を定義するintermediateモデル</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7142,7 +7145,7 @@
           <t>月・月内週番号・日付フラグ・デシル区分ごとの実績分位点を施設別に付与したintermediateモデル</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7184,7 +7187,7 @@
           <t>施設・月・曜日・日付フラグごとのZスコアの平均を算出したintermediateモデル</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7226,7 +7229,7 @@
           <t>施設・月・月内週番号・日付フラグごとの標準目標値とチャレンジ目標値を算出するintermediateモデル</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7268,7 +7271,7 @@
           <t>2025年と2026年の日別の目標値を施設*月*週番号*日付フラグ粒度で格納するファクトテーブル</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>

--- a/docs/テーブル定義書.xlsx
+++ b/docs/テーブル定義書.xlsx
@@ -217,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -279,6 +279,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -855,7 +858,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.40000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>raw_facility_actuals</t>
         </is>
@@ -1488,7 +1491,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.40000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>raw_venue_performance</t>
         </is>
@@ -2613,7 +2616,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.40000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>int_facility_actuals</t>
         </is>
@@ -3238,7 +3241,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.40000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>int_facility_daily_actual</t>
         </is>
@@ -3903,7 +3906,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.40000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>int_benchmark_periods</t>
         </is>
@@ -4293,8 +4296,8 @@
     <col width="10" customWidth="1" style="14" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52.60000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="36.40000000000001" customHeight="1" s="14">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>int_facility_event_decile_avg_actual</t>
         </is>
@@ -4959,7 +4962,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.40000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>int_event_decile_benchmark</t>
         </is>
@@ -5727,8 +5730,8 @@
     <col width="10" customWidth="1" style="14" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="68.80000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="36.40000000000001" customHeight="1" s="14">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>int_facility_monthly_dateflag_deviation_zscore</t>
         </is>
@@ -6086,8 +6089,8 @@
     <col width="10" customWidth="1" style="14" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="68.80000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="36.40000000000001" customHeight="1" s="14">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>int_facility_monthly_weekday_dateflag_deviation_zscore</t>
         </is>
@@ -6467,8 +6470,8 @@
     <col width="10" customWidth="1" style="14" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52.60000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="36.40000000000001" customHeight="1" s="14">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>int_facility_event_decile_mapping</t>
         </is>
@@ -6787,7 +6790,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="52.60000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>テーブル一覧</t>
         </is>
@@ -6840,7 +6843,7 @@
           <t>施設マスタのrawモデル。スプレッドシート由来の施設情報を保持する。</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -6865,7 +6868,7 @@
           <t>施設別・日別の偏差値ベースZスコアrawモデル</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -6890,7 +6893,7 @@
           <t>施設別・日付フラグ別の人流合計およびデシル区分rawモデル</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -6915,7 +6918,7 @@
           <t>日付マスタのrawモデル</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -6940,7 +6943,7 @@
           <t>日付マスタのrawモデル</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -6965,7 +6968,7 @@
           <t>日付マスタのrawモデル</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -6990,7 +6993,7 @@
           <t>施設名マッピングのrawモデル。施設名の表記ゆれを統一するためのマッピング情報を保持する。</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7015,7 +7018,7 @@
           <t>施設別・日付別実績のrawモデル</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7040,7 +7043,7 @@
           <t>会場別・日別実績のrawモデル</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7061,7 +7064,7 @@
           <t>施設別・日付別実績のintermediateモデル</t>
         </is>
       </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7082,7 +7085,7 @@
           <t>施設別・日別実績に施設属性と日付属性を付与したintermediateモデル</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7103,7 +7106,7 @@
           <t>ベンチマーク期間を定義するintermediateモデル</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7124,7 +7127,7 @@
           <t>施設・月・月内週番号・日付フラグ・デシル区分ごとの平均実績intermediateモデル</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7145,7 +7148,7 @@
           <t>月・月内週番号・日付フラグ・デシル区分ごとの実績分位点を施設別に付与したintermediateモデル</t>
         </is>
       </c>
-      <c r="E17" s="24" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7166,7 +7169,7 @@
           <t>施設・月・日付フラグごとのZスコアの平均を算出したintermediateモデル</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7187,7 +7190,7 @@
           <t>施設・月・曜日・日付フラグごとのZスコアの平均を算出したintermediateモデル</t>
         </is>
       </c>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7208,7 +7211,7 @@
           <t>施設・月・月内週番号・日付フラグごとのデシルランク割当intermediateモデル</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7229,7 +7232,7 @@
           <t>施設・月・月内週番号・日付フラグごとの標準目標値とチャレンジ目標値を算出するintermediateモデル</t>
         </is>
       </c>
-      <c r="E21" s="24" t="inlineStr">
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7250,7 +7253,7 @@
           <t>日別の目標値を施設*月*週番号*日付フラグ粒度で格納するファクトテーブル</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7271,7 +7274,7 @@
           <t>2025年と2026年の日別の目標値を施設*月*週番号*日付フラグ粒度で格納するファクトテーブル</t>
         </is>
       </c>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7292,7 +7295,7 @@
           <t>2026年と2027年の日別の目標値を格納するファクトテーブル</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>テーブル定義書</t>
         </is>
@@ -7354,8 +7357,8 @@
     <col width="10" customWidth="1" style="14" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52.60000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="36.40000000000001" customHeight="1" s="14">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>int_facility_event_planning_snapshot</t>
         </is>
@@ -8261,8 +8264,8 @@
     <col width="10" customWidth="1" style="14" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52.60000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="36.40000000000001" customHeight="1" s="14">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>fact_facility_performance_slots</t>
         </is>
@@ -9063,8 +9066,8 @@
     <col width="10" customWidth="1" style="14" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52.60000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="36.40000000000001" customHeight="1" s="14">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>fact_facility_performance_slots_2025_2026</t>
         </is>
@@ -9865,8 +9868,8 @@
     <col width="10" customWidth="1" style="14" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52.60000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="36.40000000000001" customHeight="1" s="14">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>fact_facility_performance_slots_2026_2027</t>
         </is>
@@ -10703,7 +10706,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.40000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>raw_facility_master</t>
         </is>
@@ -11079,8 +11082,8 @@
     <col width="10" customWidth="1" style="14" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52.60000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="36.40000000000001" customHeight="1" s="14">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>raw_facility_daily_deviation_zscore</t>
         </is>
@@ -11522,8 +11525,8 @@
     <col width="10" customWidth="1" style="14" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="68.80000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="36.40000000000001" customHeight="1" s="14">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>raw_facility_foot_traffic_avg_and_decile_by_flag</t>
         </is>
@@ -12421,7 +12424,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.40000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>raw_date_master</t>
         </is>
@@ -13167,7 +13170,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.40000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>raw_date_master_2025_2026</t>
         </is>
@@ -13780,7 +13783,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.40000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>raw_date_master_2026_2027</t>
         </is>
@@ -14393,7 +14396,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="36.40000000000001" customHeight="1" s="14">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>raw_facility_name_mappings</t>
         </is>
